--- a/2025-jonghap.xlsx
+++ b/2025-jonghap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/highmac/SnuBaseball/SnuBaseball-back/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10125A03-F42F-654B-B073-159C404D270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF3F48C-EF24-894C-9A72-C92ABAE6BAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="3200" windowWidth="29400" windowHeight="18400" xr2:uid="{1B457AFA-6E1C-D440-A48D-2A40A7C0C09B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" xr2:uid="{1B457AFA-6E1C-D440-A48D-2A40A7C0C09B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="685">
   <si>
     <t>인문대학</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -1206,9 +1206,6 @@
   </si>
   <si>
     <t>김수민</t>
-  </si>
-  <si>
-    <t>이상현</t>
   </si>
   <si>
     <t>조성훈</t>
@@ -1931,26 +1928,6 @@
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>021-14610</t>
-    </r>
-  </si>
-  <si>
-    <t>유승현</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>의대</t>
   </si>
   <si>
@@ -2535,13 +2512,51 @@
   </si>
   <si>
     <t>teamName</t>
+  </si>
+  <si>
+    <t>박지환</t>
+  </si>
+  <si>
+    <t>2021-14118</t>
+  </si>
+  <si>
+    <t>박준형</t>
+  </si>
+  <si>
+    <t>공과대학</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터공학부</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시은</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021-27545</t>
+  </si>
+  <si>
+    <t>김동윤</t>
+  </si>
+  <si>
+    <t>음악대학</t>
+  </si>
+  <si>
+    <t>피아노학과</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>고재윤</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2608,8 +2623,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2622,8 +2643,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2728,19 +2755,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2792,10 +2829,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2804,7 +2844,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2812,12 +2861,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -2852,6 +2895,12 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2866,15 +2915,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04CE23D7-CD6F-5748-814F-71E024B0DFD7}" name="Table1" displayName="Table1" ref="A1:F352" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:F352" xr:uid="{04CE23D7-CD6F-5748-814F-71E024B0DFD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{04CE23D7-CD6F-5748-814F-71E024B0DFD7}" name="Table1" displayName="Table1" ref="A1:F356" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F356" xr:uid="{04CE23D7-CD6F-5748-814F-71E024B0DFD7}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{AEFB1F08-5055-6B49-BAB4-5BBBAAF12191}" name="college" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{C903CF73-1936-A845-90CC-59CD1D724B4D}" name="department" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{CEB3BB08-A95C-D543-BBFC-93CB9B03ABBC}" name="studentId" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{31936F81-BC41-EE44-8BB9-9A82EB8B7A9F}" name="name" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{B4DD1503-C7C2-3D4E-9C61-58FF786DF9FA}" name="isWildcard" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{8B943BEC-FB98-944D-B67B-C6AFBD46CF7C}" name="teamName" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{AEFB1F08-5055-6B49-BAB4-5BBBAAF12191}" name="college" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C903CF73-1936-A845-90CC-59CD1D724B4D}" name="department" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{CEB3BB08-A95C-D543-BBFC-93CB9B03ABBC}" name="studentId" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{31936F81-BC41-EE44-8BB9-9A82EB8B7A9F}" name="name" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{B4DD1503-C7C2-3D4E-9C61-58FF786DF9FA}" name="isWildcard" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{8B943BEC-FB98-944D-B67B-C6AFBD46CF7C}" name="teamName" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3197,27 +3246,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF153CE9-800F-D84F-B073-7AEFBE12F1EC}">
-  <dimension ref="A1:F352"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3236,7 +3285,7 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3256,7 +3305,7 @@
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3276,7 +3325,7 @@
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3296,7 +3345,7 @@
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3316,7 +3365,7 @@
       <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3336,7 +3385,7 @@
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3356,7 +3405,7 @@
       <c r="E8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3376,7 +3425,7 @@
       <c r="E9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3396,7 +3445,7 @@
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3416,7 +3465,7 @@
       <c r="E11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3436,7 +3485,7 @@
       <c r="E12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3456,7 +3505,7 @@
       <c r="E13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3476,7 +3525,7 @@
       <c r="E14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3496,7 +3545,7 @@
       <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3516,7 +3565,7 @@
       <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3536,7 +3585,7 @@
       <c r="E17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3556,7 +3605,7 @@
       <c r="E18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3576,7 +3625,7 @@
       <c r="E19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3596,47 +3645,47 @@
       <c r="E20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3656,7 +3705,7 @@
       <c r="E23" t="s">
         <v>116</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3676,7 +3725,7 @@
       <c r="E24" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3696,7 +3745,7 @@
       <c r="E25" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3716,7 +3765,7 @@
       <c r="E26" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3736,7 +3785,7 @@
       <c r="E27" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3756,7 +3805,7 @@
       <c r="E28" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3776,7 +3825,7 @@
       <c r="E29" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3796,7 +3845,7 @@
       <c r="E30" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3816,7 +3865,7 @@
       <c r="E31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3836,7 +3885,7 @@
       <c r="E32" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3856,7 +3905,7 @@
       <c r="E33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3876,7 +3925,7 @@
       <c r="E34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3896,7 +3945,7 @@
       <c r="E35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3916,7 +3965,7 @@
       <c r="E36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3936,7 +3985,7 @@
       <c r="E37" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3956,7 +4005,7 @@
       <c r="E38" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3976,7 +4025,7 @@
       <c r="E39" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3996,7 +4045,7 @@
       <c r="E40" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4016,7 +4065,7 @@
       <c r="E41" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4036,7 +4085,7 @@
       <c r="E42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4056,7 +4105,7 @@
       <c r="E43" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4076,7 +4125,7 @@
       <c r="E44" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4096,7 +4145,7 @@
       <c r="E45" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4116,7 +4165,7 @@
       <c r="E46" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4136,7 +4185,7 @@
       <c r="E47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4156,7 +4205,7 @@
       <c r="E48" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4176,7 +4225,7 @@
       <c r="E49" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4187,16 +4236,16 @@
       <c r="B50" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="3">
         <v>202515986</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4216,7 +4265,7 @@
       <c r="E51" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4236,7 +4285,7 @@
       <c r="E52" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4256,7 +4305,7 @@
       <c r="E53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4276,7 +4325,7 @@
       <c r="E54" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4296,7 +4345,7 @@
       <c r="E55" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4316,408 +4365,408 @@
       <c r="E56" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>347</v>
+      <c r="E57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>347</v>
+      <c r="E58" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>347</v>
+      <c r="E59" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>347</v>
+      <c r="E60" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>347</v>
+      <c r="F61" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="6">
         <v>202315395</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>347</v>
+      <c r="E62" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="6">
         <v>202010178</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>347</v>
+      <c r="E63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="6">
         <v>202329850</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>347</v>
+      <c r="F64" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E65" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>347</v>
+      <c r="E65" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="6">
         <v>202311104</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>347</v>
+      <c r="E66" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>347</v>
+      <c r="F67" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>202416615</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>347</v>
+      <c r="E68" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="6">
         <v>202510364</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>347</v>
+      <c r="E69" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="6">
         <v>202019993</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>347</v>
+      <c r="E70" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E71" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>347</v>
+      <c r="E71" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="6">
         <v>202116156</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E72" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>347</v>
+      <c r="E72" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="6">
         <v>202018782</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>347</v>
+      <c r="F73" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>347</v>
+      <c r="F74" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>347</v>
+      <c r="E75" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>347</v>
+      <c r="F76" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -4736,7 +4785,7 @@
       <c r="E77" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4756,7 +4805,7 @@
       <c r="E78" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4776,7 +4825,7 @@
       <c r="E79" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4796,7 +4845,7 @@
       <c r="E80" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4816,7 +4865,7 @@
       <c r="E81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4836,7 +4885,7 @@
       <c r="E82" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4856,7 +4905,7 @@
       <c r="E83" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4876,7 +4925,7 @@
       <c r="E84" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4896,7 +4945,7 @@
       <c r="E85" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4916,7 +4965,7 @@
       <c r="E86" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4936,7 +4985,7 @@
       <c r="E87" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4956,7 +5005,7 @@
       <c r="E88" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4976,7 +5025,7 @@
       <c r="E89" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4996,7 +5045,7 @@
       <c r="E90" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5016,7 +5065,7 @@
       <c r="E91" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5036,7 +5085,7 @@
       <c r="E92" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5056,7 +5105,7 @@
       <c r="E93" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5076,7 +5125,7 @@
       <c r="E94" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5096,7 +5145,7 @@
       <c r="E95" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5116,7 +5165,7 @@
       <c r="E96" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5136,7 +5185,7 @@
       <c r="E97" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5156,7 +5205,7 @@
       <c r="E98" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5176,7 +5225,7 @@
       <c r="E99" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5196,7 +5245,7 @@
       <c r="E100" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5216,7 +5265,7 @@
       <c r="E101" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5236,7 +5285,7 @@
       <c r="E102" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5256,7 +5305,7 @@
       <c r="E103" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5276,7 +5325,7 @@
       <c r="E104" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5296,7 +5345,7 @@
       <c r="E105" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5316,7 +5365,7 @@
       <c r="E106" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5336,7 +5385,7 @@
       <c r="E107" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5356,7 +5405,7 @@
       <c r="E108" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5376,7 +5425,7 @@
       <c r="E109" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5396,7 +5445,7 @@
       <c r="E110" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5416,7 +5465,7 @@
       <c r="E111" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5436,107 +5485,107 @@
       <c r="E112" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="3">
         <v>201625763</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C114" s="1">
-        <v>202513118</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>267</v>
+      <c r="A114" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C114" s="24">
+        <v>202129853</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>674</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F114" s="23" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="C115" s="1">
-        <v>202515752</v>
+        <v>202513118</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>53</v>
+        <v>682</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>268</v>
+        <v>683</v>
       </c>
       <c r="C116" s="1">
-        <v>202512171</v>
+        <v>202015707</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>270</v>
+        <v>684</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="23" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C117" s="1">
-        <v>202018975</v>
+        <v>202515752</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="1" t="s">
         <v>293</v>
       </c>
     </row>
@@ -5545,158 +5594,158 @@
         <v>53</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C118" s="1">
-        <v>202322714</v>
+        <v>202512171</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F118" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C119" s="1">
-        <v>202117939</v>
+        <v>202018975</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="C120" s="1">
-        <v>202016861</v>
+        <v>202322714</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F120" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C121" s="1">
-        <v>202412947</v>
+        <v>202117939</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="C122" s="1">
-        <v>202011802</v>
+        <v>202016861</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>280</v>
+        <v>53</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C123" s="1">
-        <v>202019898</v>
+        <v>202412947</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="C124" s="1">
-        <v>202210533</v>
+        <v>202011802</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>53</v>
+        <v>280</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C125" s="1">
-        <v>202115267</v>
+        <v>202019898</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F125" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>293</v>
       </c>
     </row>
@@ -5705,18 +5754,18 @@
         <v>126</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C126" s="1">
-        <v>202510734</v>
+        <v>202210533</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="1" t="s">
         <v>293</v>
       </c>
     </row>
@@ -5728,35 +5777,35 @@
         <v>285</v>
       </c>
       <c r="C127" s="1">
-        <v>202113070</v>
+        <v>202115267</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="C128" s="1">
-        <v>202419250</v>
+        <v>202510734</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="1" t="s">
         <v>293</v>
       </c>
     </row>
@@ -5765,79 +5814,79 @@
         <v>53</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="C129" s="1">
-        <v>202427748</v>
+        <v>202113070</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F129" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C130" s="4">
-        <v>202317123</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="3" t="s">
+      <c r="A130" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C130" s="1">
+        <v>202419250</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="C131" s="1">
-        <v>202310542</v>
+        <v>202427748</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>319</v>
+        <v>75</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C132" s="1">
-        <v>202415355</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>319</v>
+      <c r="A132" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C132" s="3">
+        <v>202317123</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
@@ -5848,56 +5897,56 @@
         <v>294</v>
       </c>
       <c r="C133" s="1">
-        <v>202515196</v>
+        <v>202310542</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F133" s="3" t="s">
-        <v>319</v>
+      <c r="F133" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>298</v>
+        <v>173</v>
       </c>
       <c r="C134" s="1">
-        <v>202516881</v>
+        <v>202415355</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F134" s="3" t="s">
-        <v>319</v>
+      <c r="F134" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1">
-        <v>202418123</v>
+        <v>202515196</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F135" s="3" t="s">
-        <v>319</v>
+      <c r="F135" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -5905,119 +5954,119 @@
         <v>200</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="C136" s="1">
-        <v>202210286</v>
+        <v>202516881</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F136" s="3" t="s">
-        <v>319</v>
+      <c r="F136" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C137" s="1">
-        <v>202413582</v>
+        <v>202418123</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F137" s="3" t="s">
-        <v>319</v>
+      <c r="F137" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C138" s="1">
-        <v>202212368</v>
+        <v>202210286</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F138" s="3" t="s">
-        <v>319</v>
+      <c r="F138" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>188</v>
+        <v>304</v>
       </c>
       <c r="C139" s="1">
-        <v>202015976</v>
+        <v>202413582</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F139" s="3" t="s">
-        <v>319</v>
+      <c r="F139" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>294</v>
+        <v>180</v>
       </c>
       <c r="C140" s="1">
-        <v>202517567</v>
+        <v>202212368</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F140" s="3" t="s">
-        <v>319</v>
+      <c r="F140" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>294</v>
+        <v>188</v>
       </c>
       <c r="C141" s="1">
-        <v>202514082</v>
+        <v>202015976</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F141" s="3" t="s">
-        <v>319</v>
+      <c r="F141" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
@@ -6028,16 +6077,16 @@
         <v>294</v>
       </c>
       <c r="C142" s="1">
-        <v>202512889</v>
+        <v>202517567</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F142" s="3" t="s">
-        <v>319</v>
+      <c r="F142" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
@@ -6045,39 +6094,39 @@
         <v>200</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C143" s="1">
-        <v>202511107</v>
+        <v>202514082</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F143" s="3" t="s">
-        <v>319</v>
+      <c r="F143" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="C144" s="1">
-        <v>202510232</v>
+        <v>202512889</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F144" s="3" t="s">
-        <v>319</v>
+      <c r="F144" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
@@ -6085,19 +6134,19 @@
         <v>200</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C145" s="1">
-        <v>202312228</v>
+        <v>202511107</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F145" s="3" t="s">
-        <v>319</v>
+      <c r="F145" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
@@ -6108,36 +6157,36 @@
         <v>173</v>
       </c>
       <c r="C146" s="1">
-        <v>202510031</v>
+        <v>202510232</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F146" s="3" t="s">
-        <v>319</v>
+      <c r="F146" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="C147" s="1">
-        <v>202210065</v>
+        <v>202510031</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F147" s="3" t="s">
-        <v>319</v>
+      <c r="F147" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
@@ -6145,79 +6194,79 @@
         <v>200</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>201</v>
+        <v>294</v>
       </c>
       <c r="C148" s="1">
-        <v>202310596</v>
+        <v>202210065</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F148" s="3" t="s">
-        <v>319</v>
+      <c r="F148" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C149" s="1">
+        <v>202310596</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C150" s="1">
         <v>201829929</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D150" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C151" s="3">
+        <v>201915940</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E149" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C150" s="4">
-        <v>201915940</v>
-      </c>
-      <c r="D150" s="4" t="s">
+      <c r="E151" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C151" s="1">
-        <v>202125015</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
@@ -6225,139 +6274,139 @@
         <v>169</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C152" s="1">
+        <v>202125015</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C152" s="1">
-        <v>202125601</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>346</v>
+        <v>321</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>324</v>
+        <v>169</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C153" s="1">
-        <v>201715129</v>
+        <v>202125601</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>346</v>
+        <v>321</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>169</v>
+        <v>323</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C154" s="1">
-        <v>202429632</v>
+        <v>201715129</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>346</v>
+        <v>113</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="C155" s="1">
-        <v>202325810</v>
+        <v>202429632</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>346</v>
+        <v>321</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>320</v>
+        <v>108</v>
       </c>
       <c r="C156" s="1">
-        <v>202026924</v>
+        <v>202325810</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>346</v>
+        <v>75</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>330</v>
+        <v>169</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C157" s="1">
-        <v>202521336</v>
+        <v>202026924</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>346</v>
+        <v>321</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>76</v>
+        <v>329</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="C158" s="1">
-        <v>202515675</v>
+        <v>202521336</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>346</v>
+        <v>321</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
@@ -6368,16 +6417,16 @@
         <v>108</v>
       </c>
       <c r="C159" s="1">
-        <v>202114312</v>
+        <v>202515675</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F159" s="3" t="s">
-        <v>346</v>
+      <c r="F159" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
@@ -6388,16 +6437,16 @@
         <v>108</v>
       </c>
       <c r="C160" s="1">
-        <v>202412615</v>
+        <v>202114312</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F160" s="3" t="s">
-        <v>346</v>
+      <c r="F160" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
@@ -6408,156 +6457,156 @@
         <v>108</v>
       </c>
       <c r="C161" s="1">
+        <v>202412615</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C162" s="1">
         <v>202015891</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="D162" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C163" s="1">
+        <v>202216862</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E161" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" s="13" t="s">
+      <c r="E163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B162" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C162" s="1">
-        <v>202216862</v>
-      </c>
-      <c r="D162" s="1" t="s">
+      <c r="B164" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C164" s="1">
+        <v>202515488</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" s="13" t="s">
+      <c r="E164" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B163" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C163" s="1">
-        <v>202515488</v>
-      </c>
-      <c r="D163" s="1" t="s">
+      <c r="B165" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C165" s="1">
+        <v>202110354</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" s="13" t="s">
+      <c r="E165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B164" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C164" s="1">
-        <v>202110354</v>
-      </c>
-      <c r="D164" s="1" t="s">
+      <c r="B166" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C166" s="1">
+        <v>202513479</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E164" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" s="13" t="s">
+      <c r="E166" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B165" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C165" s="1">
-        <v>202513479</v>
-      </c>
-      <c r="D165" s="1" t="s">
+      <c r="B167" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C167" s="1">
+        <v>202512142</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A166" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B166" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C166" s="1">
-        <v>202512142</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C167" s="1">
-        <v>202122763</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="E167" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>346</v>
+        <v>4</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="C168" s="1">
-        <v>202322999</v>
+        <v>202122763</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>346</v>
+        <v>113</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
@@ -6568,16 +6617,16 @@
         <v>108</v>
       </c>
       <c r="C169" s="1">
-        <v>202330317</v>
+        <v>202322999</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>346</v>
+        <v>75</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
@@ -6588,1936 +6637,1936 @@
         <v>108</v>
       </c>
       <c r="C170" s="1">
+        <v>202330317</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C171" s="1">
         <v>202326189</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="D171" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E170" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A171" s="9" t="s">
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B172" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C171" s="9" t="s">
+      <c r="C172" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D172" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="D171" s="9" t="s">
+      <c r="E172" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B173" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="E171" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F171" s="3" t="s">
+      <c r="C173" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C186" s="8">
+        <v>202215057</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="45" x14ac:dyDescent="0.2">
+      <c r="A192" s="13" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A172" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B172" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="D172" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="E172" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172" s="3" t="s">
+      <c r="B192" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="C192" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="D192" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="E192" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A193" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B193" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="C193" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="D193" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E193" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A194" s="13" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A173" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B173" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E173" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A174" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B174" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="C174" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D174" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="E174" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A175" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="B175" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E175" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A176" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="E176" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F176" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A177" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="E177" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A178" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B178" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="E178" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A179" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B179" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="E179" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A180" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B180" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C180" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="E180" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A181" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="D181" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="E181" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A182" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="D182" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="E182" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A183" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D183" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E183" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A184" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="D184" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="E184" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A185" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C185" s="9">
-        <v>202215057</v>
-      </c>
-      <c r="D185" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E185" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A186" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B186" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="D186" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E186" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A187" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="C187" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D187" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="E187" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A188" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B188" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="E188" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A189" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="D189" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="E189" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A190" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="D190" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="E190" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="45" x14ac:dyDescent="0.2">
-      <c r="A191" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B191" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C191" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="D191" s="15" t="s">
+      <c r="B194" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="C194" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="D194" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="E194" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A195" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="B195" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="C195" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="D195" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="E195" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="B196" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="C196" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E196" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A197" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="B197" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="C197" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D197" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E197" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A198" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="E191" s="16" t="s">
+      <c r="B198" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="D198" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E198" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F191" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A192" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B192" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="C192" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="D192" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="E192" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A193" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B193" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="C193" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="D193" s="15" t="s">
+      <c r="F198" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A199" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="B199" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="C199" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="D199" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="E199" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A200" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="B200" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C200" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D200" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="E200" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A201" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B201" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="C201" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="D201" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="E201" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="B202" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="C202" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="D202" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="E202" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A203" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B203" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="C203" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="D203" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="E203" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="B204" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="C204" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="D204" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E204" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B205" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C205" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="D205" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="E205" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A206" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C206" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="D206" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="E206" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A207" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B207" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="C207" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D207" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="E207" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A208" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B208" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="C208" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D208" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="E208" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C209" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="D209" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="E209" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="E193" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A194" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B194" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="C194" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="D194" s="15" t="s">
+      <c r="B210" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="C210" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="D210" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="E210" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="B211" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D211" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="E211" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="B212" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="C212" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D212" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="E212" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="E194" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A195" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="B195" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C195" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="D195" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="E195" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A196" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="B196" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="C196" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="D196" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="E196" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A197" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B197" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C197" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="D197" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="E197" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A198" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="B198" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="C198" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="D198" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="E198" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A199" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="B199" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C199" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D199" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="E199" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A200" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="B200" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="C200" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="D200" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="E200" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A201" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="B201" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C201" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="D201" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="E201" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A202" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B202" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C202" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="D202" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="E202" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A203" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="B203" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="C203" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="D203" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="E203" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A204" s="14" t="s">
-        <v>442</v>
-      </c>
-      <c r="B204" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="C204" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="D204" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="E204" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A205" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B205" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C205" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="D205" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="E205" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A206" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B206" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="C206" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="D206" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="E206" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A207" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B207" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="C207" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="D207" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="E207" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A208" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="B208" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="C208" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="D208" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="E208" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A209" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B209" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C209" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="D209" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="E209" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A210" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="B210" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="C210" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="D210" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="E210" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A211" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="B211" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="C211" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="D211" s="15" t="s">
+      <c r="B213" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="E211" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A212" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="B212" s="18" t="s">
+      <c r="C213" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="C212" s="18" t="s">
+      <c r="D213" s="17" t="s">
         <v>466</v>
       </c>
-      <c r="D212" s="18" t="s">
+      <c r="E213" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="E212" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A213" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E213" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>209</v>
-      </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" s="19" t="s">
+      <c r="A214" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="E214" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F214" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E214" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F214" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A215" s="19" t="s">
+      <c r="A215" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E215" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F215" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E215" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A216" s="19" t="s">
+      <c r="A216" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E216" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F216" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E216" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F216" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A217" s="19" t="s">
+      <c r="A217" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E217" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F217" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E217" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A218" s="19" t="s">
+      <c r="A218" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E218" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F218" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="E218" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A219" s="19" t="s">
+      <c r="A219" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E219" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F219" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="E219" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A220" s="19" t="s">
+      <c r="A220" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E220" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F220" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E220" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F220" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A221" s="19" t="s">
+      <c r="A221" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E221" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F221" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E221" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A222" s="19" t="s">
+      <c r="A222" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E222" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F222" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E222" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A223" s="19" t="s">
+      <c r="A223" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E223" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F223" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="E223" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A224" s="19" t="s">
+      <c r="A224" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E224" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F224" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E224" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F224" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A225" s="19" t="s">
+      <c r="A225" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E225" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F225" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E225" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F225" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A226" s="19" t="s">
+      <c r="A226" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E226" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F226" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="E226" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F226" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A227" s="19" t="s">
+      <c r="A227" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C227" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E227" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="E228" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B229" s="19" t="s">
         <v>498</v>
       </c>
-      <c r="E227" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F227" s="3" t="s">
+      <c r="C229" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="D229" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="E229" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A228" s="19" t="s">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B228" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="C228" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="D228" s="20" t="s">
+      <c r="B230" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="C230" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="E228" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F228" s="3" t="s">
+      <c r="D230" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="E230" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A229" s="19" t="s">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B229" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="C229" s="20" t="s">
+      <c r="B231" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C231" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="D231" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="D229" s="20" t="s">
-        <v>503</v>
-      </c>
-      <c r="E229" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F229" s="3" t="s">
+      <c r="E231" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B230" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="C230" s="20" t="s">
-        <v>504</v>
-      </c>
-      <c r="D230" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="E230" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A231" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C231" s="1">
-        <v>201910560</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>510</v>
+        <v>191</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C232" s="1">
-        <v>201916763</v>
+        <v>209</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>506</v>
+        <v>676</v>
+      </c>
+      <c r="E232" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C233" s="1">
-        <v>202117595</v>
+        <v>201910560</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F233" s="3" t="s">
-        <v>506</v>
+      <c r="F233" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B234" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C234" s="1">
+        <v>201916763</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C234" s="1">
-        <v>202012516</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="E234" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F234" s="3" t="s">
-        <v>506</v>
+      <c r="F234" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C235" s="1">
-        <v>202115760</v>
+        <v>202117595</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F235" s="3" t="s">
-        <v>506</v>
+      <c r="F235" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C236" s="1">
+        <v>202012516</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C236" s="1">
-        <v>202114695</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E236" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F236" s="3" t="s">
-        <v>506</v>
+      <c r="F236" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C237" s="1">
-        <v>202211194</v>
+        <v>202115760</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F237" s="3" t="s">
-        <v>506</v>
+      <c r="F237" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C238" s="1">
-        <v>202218369</v>
+        <v>202114695</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F238" s="3" t="s">
-        <v>506</v>
+      <c r="F238" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C239" s="1">
-        <v>202216410</v>
+        <v>202211194</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F239" s="3" t="s">
-        <v>506</v>
+      <c r="F239" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C240" s="1">
-        <v>202218738</v>
+        <v>202218369</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F240" s="3" t="s">
-        <v>506</v>
+      <c r="F240" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="C241" s="1">
-        <v>202314713</v>
+        <v>202216410</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F241" s="3" t="s">
-        <v>506</v>
+      <c r="F241" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C242" s="20">
-        <v>202318250</v>
+        <v>505</v>
+      </c>
+      <c r="C242" s="1">
+        <v>202218738</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F242" s="3" t="s">
-        <v>506</v>
+      <c r="F242" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C243" s="1">
-        <v>202317502</v>
+        <v>202314713</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F243" s="3" t="s">
-        <v>506</v>
+      <c r="F243" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C244" s="1">
-        <v>202312309</v>
+        <v>517</v>
+      </c>
+      <c r="C244" s="19">
+        <v>202318250</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F244" s="3" t="s">
-        <v>506</v>
+      <c r="F244" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C245" s="1">
+        <v>202317502</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C245" s="20">
-        <v>202413491</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="E245" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F245" s="3" t="s">
-        <v>506</v>
+      <c r="F245" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C246" s="1">
-        <v>202418026</v>
+        <v>202312309</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F246" s="3" t="s">
-        <v>506</v>
+      <c r="F246" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C247" s="1">
-        <v>202419302</v>
+        <v>517</v>
+      </c>
+      <c r="C247" s="19">
+        <v>202413491</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F247" s="3" t="s">
-        <v>506</v>
+      <c r="F247" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C248" s="1">
-        <v>202416774</v>
+        <v>202418026</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F248" s="3" t="s">
-        <v>506</v>
+      <c r="F248" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C249" s="1">
-        <v>202412725</v>
+        <v>202419302</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F249" s="3" t="s">
-        <v>506</v>
+      <c r="F249" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C250" s="1">
-        <v>202410998</v>
+        <v>202416774</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F250" s="3" t="s">
-        <v>506</v>
+      <c r="F250" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C251" s="20">
-        <v>202418521</v>
+        <v>517</v>
+      </c>
+      <c r="C251" s="1">
+        <v>202412725</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F251" s="3" t="s">
-        <v>506</v>
+      <c r="F251" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C252" s="1">
-        <v>202414351</v>
+        <v>202410998</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F252" s="3" t="s">
-        <v>506</v>
+      <c r="F252" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C253" s="1">
-        <v>202417566</v>
+        <v>517</v>
+      </c>
+      <c r="C253" s="19">
+        <v>202418521</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F253" s="3" t="s">
-        <v>506</v>
+      <c r="F253" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C254" s="1">
-        <v>202515763</v>
+        <v>202414351</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F254" s="3" t="s">
-        <v>506</v>
+      <c r="F254" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C255" s="1">
-        <v>202512873</v>
+        <v>202417566</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F255" s="3" t="s">
-        <v>506</v>
+      <c r="F255" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C256" s="1">
-        <v>202515877</v>
+        <v>202515763</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F256" s="3" t="s">
-        <v>506</v>
+      <c r="F256" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A257" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="B257" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="C257" s="4">
-        <v>202517780</v>
-      </c>
-      <c r="D257" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="E257" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>506</v>
+      <c r="A257" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C257" s="1">
+        <v>202512873</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>280</v>
+        <v>507</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="C258" s="1">
-        <v>202414600</v>
+        <v>202515877</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F258" s="3" t="s">
-        <v>580</v>
+      <c r="F258" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A259" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="C259" s="1">
-        <v>202010719</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>580</v>
+      <c r="A259" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C259" s="3">
+        <v>202517780</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>542</v>
+        <v>280</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C260" s="1">
-        <v>202419904</v>
+        <v>202414600</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F260" s="3" t="s">
-        <v>580</v>
+      <c r="F260" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>280</v>
+        <v>71</v>
       </c>
       <c r="B261" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C261" s="1">
+        <v>202010719</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C261" s="1">
-        <v>202516511</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="E261" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F261" s="3" t="s">
-        <v>580</v>
+      <c r="F261" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>280</v>
+        <v>539</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C262" s="1">
-        <v>202010482</v>
+        <v>202419904</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>580</v>
+        <v>4</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>546</v>
+        <v>280</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C263" s="1">
-        <v>202413217</v>
+        <v>202516511</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F263" s="3" t="s">
-        <v>580</v>
+      <c r="F263" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>126</v>
+        <v>280</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="C264" s="1">
-        <v>202418817</v>
+        <v>202010482</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>580</v>
+        <v>100</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>280</v>
+        <v>543</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C265" s="1">
-        <v>202011302</v>
+        <v>202413217</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F265" s="3" t="s">
-        <v>580</v>
+      <c r="F265" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>80</v>
+        <v>546</v>
       </c>
       <c r="C266" s="1">
-        <v>202417627</v>
+        <v>202418817</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F266" s="3" t="s">
-        <v>580</v>
+      <c r="F266" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.2">
@@ -8525,39 +8574,39 @@
         <v>280</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C267" s="1">
-        <v>202015739</v>
+        <v>202011302</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F267" s="3" t="s">
-        <v>580</v>
+      <c r="F267" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>280</v>
+        <v>76</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>538</v>
+        <v>80</v>
       </c>
       <c r="C268" s="1">
-        <v>202012648</v>
+        <v>202417627</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F268" s="3" t="s">
-        <v>580</v>
+      <c r="F268" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.2">
@@ -8565,19 +8614,19 @@
         <v>280</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C269" s="1">
-        <v>202017533</v>
+        <v>202015739</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F269" s="3" t="s">
-        <v>580</v>
+      <c r="F269" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
@@ -8585,99 +8634,99 @@
         <v>280</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C270" s="1">
-        <v>202212798</v>
+        <v>202012648</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F270" s="3" t="s">
-        <v>580</v>
+      <c r="F270" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>557</v>
+        <v>280</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="C271" s="1">
-        <v>202428369</v>
+        <v>202017533</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>580</v>
+        <v>4</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>101</v>
+        <v>535</v>
       </c>
       <c r="C272" s="1">
-        <v>202217682</v>
+        <v>202212798</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F272" s="3" t="s">
-        <v>580</v>
+      <c r="F272" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>280</v>
+        <v>554</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="C273" s="1">
-        <v>202511607</v>
+        <v>202428369</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F273" s="3" t="s">
-        <v>580</v>
+        <v>75</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>280</v>
+        <v>101</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>538</v>
+        <v>101</v>
       </c>
       <c r="C274" s="1">
-        <v>201915124</v>
+        <v>202217682</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F274" s="3" t="s">
-        <v>580</v>
+      <c r="F274" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
@@ -8685,19 +8734,19 @@
         <v>280</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C275" s="1">
-        <v>202511180</v>
+        <v>202511607</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F275" s="3" t="s">
-        <v>580</v>
+      <c r="F275" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.2">
@@ -8705,19 +8754,19 @@
         <v>280</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C276" s="1">
-        <v>202410685</v>
+        <v>201915124</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F276" s="3" t="s">
-        <v>580</v>
+      <c r="F276" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.2">
@@ -8725,139 +8774,139 @@
         <v>280</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C277" s="1">
-        <v>201913878</v>
+        <v>202511180</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>580</v>
+        <v>4</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>180</v>
+        <v>535</v>
       </c>
       <c r="C278" s="1">
-        <v>202415190</v>
+        <v>202410685</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F278" s="3" t="s">
-        <v>580</v>
+      <c r="F278" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="C279" s="1">
-        <v>202525578</v>
+        <v>201913878</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>580</v>
+        <v>100</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C280" s="1">
-        <v>202513963</v>
+        <v>202415190</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F280" s="3" t="s">
-        <v>580</v>
+      <c r="F280" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>350</v>
+        <v>564</v>
       </c>
       <c r="C281" s="1">
-        <v>202014306</v>
+        <v>202525578</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F281" s="3" t="s">
-        <v>580</v>
+        <v>75</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C282" s="1">
-        <v>202411104</v>
+        <v>202513963</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F282" s="3" t="s">
-        <v>580</v>
+      <c r="F282" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>572</v>
+        <v>349</v>
       </c>
       <c r="C283" s="1">
-        <v>202214617</v>
+        <v>202014306</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F283" s="3" t="s">
-        <v>580</v>
+      <c r="F283" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.2">
@@ -8865,19 +8914,19 @@
         <v>169</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C284" s="1">
-        <v>202515285</v>
+        <v>202411104</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F284" s="3" t="s">
-        <v>580</v>
+      <c r="F284" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
@@ -8885,39 +8934,39 @@
         <v>169</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>180</v>
+        <v>569</v>
       </c>
       <c r="C285" s="1">
-        <v>202513273</v>
+        <v>202214617</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F285" s="3" t="s">
-        <v>580</v>
+      <c r="F285" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C286" s="1">
-        <v>202512850</v>
+        <v>202515285</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F286" s="3" t="s">
-        <v>580</v>
+      <c r="F286" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.2">
@@ -8925,39 +8974,39 @@
         <v>169</v>
       </c>
       <c r="B287" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C287" s="1">
+        <v>202513273</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C287" s="1">
-        <v>202517411</v>
-      </c>
-      <c r="D287" s="1" t="s">
+      <c r="E287" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F287" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>572</v>
+        <v>173</v>
       </c>
       <c r="C288" s="1">
-        <v>202512084</v>
+        <v>202512850</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F288" s="3" t="s">
-        <v>580</v>
+      <c r="F288" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.2">
@@ -8965,59 +9014,59 @@
         <v>169</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C289" s="1">
-        <v>202217140</v>
+        <v>202517411</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F289" s="3" t="s">
-        <v>580</v>
+      <c r="F289" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>77</v>
+        <v>569</v>
       </c>
       <c r="C290" s="1">
-        <v>202410045</v>
+        <v>202512084</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F290" s="23" t="s">
-        <v>609</v>
+      <c r="F290" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>256</v>
+        <v>569</v>
       </c>
       <c r="C291" s="1">
-        <v>202514293</v>
+        <v>202217140</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F291" s="23" t="s">
-        <v>609</v>
+      <c r="F291" s="1" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
@@ -9025,19 +9074,19 @@
         <v>76</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="C292" s="1">
-        <v>202415193</v>
+        <v>202410045</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F292" s="23" t="s">
-        <v>609</v>
+      <c r="F292" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.2">
@@ -9048,16 +9097,16 @@
         <v>256</v>
       </c>
       <c r="C293" s="1">
-        <v>202433402</v>
+        <v>202514293</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F293" s="23" t="s">
-        <v>609</v>
+        <v>4</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
@@ -9068,16 +9117,16 @@
         <v>256</v>
       </c>
       <c r="C294" s="1">
-        <v>202316802</v>
+        <v>202415193</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>584</v>
+        <v>112</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F294" s="23" t="s">
-        <v>609</v>
+      <c r="F294" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.2">
@@ -9088,16 +9137,16 @@
         <v>256</v>
       </c>
       <c r="C295" s="1">
-        <v>202518064</v>
+        <v>202433402</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F295" s="23" t="s">
-        <v>609</v>
+        <v>75</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
@@ -9105,336 +9154,336 @@
         <v>76</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="C296" s="1">
-        <v>202326066</v>
+        <v>202316802</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F296" s="23" t="s">
-        <v>609</v>
+        <v>4</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>587</v>
+        <v>256</v>
       </c>
       <c r="C297" s="1">
-        <v>200310088</v>
+        <v>202518064</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F297" s="23" t="s">
-        <v>609</v>
+        <v>4</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>283</v>
+        <v>108</v>
       </c>
       <c r="C298" s="1">
-        <v>202219511</v>
+        <v>202326066</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F298" s="23" t="s">
-        <v>609</v>
+        <v>75</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>557</v>
+        <v>126</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C299" s="1">
-        <v>202220824</v>
+        <v>200310088</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F299" s="23" t="s">
-        <v>609</v>
+        <v>100</v>
+      </c>
+      <c r="F299" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="B300" s="1"/>
-      <c r="C300" s="22" t="s">
-        <v>592</v>
+        <v>126</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C300" s="1">
+        <v>202219511</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F300" s="23" t="s">
-        <v>609</v>
+        <v>4</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C301" s="22">
-        <v>202328243</v>
+        <v>555</v>
+      </c>
+      <c r="C301" s="1">
+        <v>202220824</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F301" s="23" t="s">
-        <v>609</v>
+      <c r="F301" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C302" s="1">
-        <v>202333139</v>
+        <v>588</v>
+      </c>
+      <c r="B302" s="1"/>
+      <c r="C302" s="21" t="s">
+        <v>589</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F302" s="23" t="s">
-        <v>609</v>
+        <v>134</v>
+      </c>
+      <c r="F302" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>598</v>
+        <v>592</v>
+      </c>
+      <c r="C303" s="21">
+        <v>202328243</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F303" s="23" t="s">
-        <v>609</v>
+      <c r="F303" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C304" s="1">
+        <v>202333139</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C304" s="1">
-        <v>202529745</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F304" s="23" t="s">
-        <v>609</v>
+      <c r="F304" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="C305" s="1">
-        <v>202427436</v>
+        <v>592</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>595</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F305" s="23" t="s">
-        <v>609</v>
+      <c r="F305" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C306" s="1">
-        <v>202326479</v>
+        <v>202529745</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F306" s="23" t="s">
-        <v>609</v>
+        <v>75</v>
+      </c>
+      <c r="F306" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>101</v>
+        <v>598</v>
       </c>
       <c r="B307" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C307" s="1">
+        <v>202427436</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F307" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="C307" s="1">
-        <v>202211598</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F307" s="23" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>76</v>
+        <v>598</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="C308" s="1">
-        <v>202515955</v>
+        <v>202326479</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F308" s="23" t="s">
-        <v>609</v>
+        <v>100</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>2</v>
+        <v>603</v>
+      </c>
+      <c r="C309" s="1">
+        <v>202211598</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>3</v>
+        <v>604</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F309" s="23" t="s">
-        <v>49</v>
+      <c r="F309" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>7</v>
+        <v>256</v>
+      </c>
+      <c r="C310" s="1">
+        <v>202515955</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>8</v>
+        <v>605</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F310" s="23" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A311" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>9</v>
+      <c r="A311" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C311" s="3">
+        <v>202514417</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="F311" s="23" t="s">
-        <v>49</v>
+        <v>606</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F312" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F312" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9446,55 +9495,55 @@
         <v>6</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F313" s="23" t="s">
+      <c r="F313" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F314" s="23" t="s">
+      <c r="F314" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F315" s="23" t="s">
+      <c r="F315" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9503,58 +9552,58 @@
         <v>5</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F316" s="23" t="s">
+      <c r="F316" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F317" s="23" t="s">
+      <c r="F317" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F318" s="23" t="s">
+      <c r="F318" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9563,38 +9612,38 @@
         <v>5</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F319" s="23" t="s">
+      <c r="F319" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F320" s="23" t="s">
+      <c r="F320" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9606,15 +9655,15 @@
         <v>6</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F321" s="23" t="s">
+      <c r="F321" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9626,55 +9675,55 @@
         <v>6</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F322" s="23" t="s">
+      <c r="F322" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F323" s="23" t="s">
+      <c r="F323" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F324" s="23" t="s">
+      <c r="F324" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9686,15 +9735,15 @@
         <v>6</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F325" s="23" t="s">
+      <c r="F325" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9703,548 +9752,631 @@
         <v>37</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F326" s="23" t="s">
+      <c r="F326" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>610</v>
+        <v>41</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>611</v>
+        <v>42</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>612</v>
+        <v>43</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F327" s="23" t="s">
+      <c r="F327" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A328" s="4" t="s">
+      <c r="A328" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B328" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="D328" s="4" t="s">
-        <v>615</v>
+      <c r="B328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F328" s="23" t="s">
+      <c r="F328" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A329" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="D329" s="4" t="s">
-        <v>617</v>
+      <c r="A329" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F329" s="23" t="s">
+      <c r="F329" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A330" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>620</v>
+      <c r="A330" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>609</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F330" s="23" t="s">
+      <c r="F330" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A331" s="24" t="s">
-        <v>621</v>
-      </c>
-      <c r="B331" s="24" t="s">
-        <v>622</v>
-      </c>
-      <c r="C331" s="24" t="s">
-        <v>623</v>
-      </c>
-      <c r="D331" s="24" t="s">
-        <v>624</v>
+      <c r="A331" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>612</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F331" s="23" t="s">
+      <c r="F331" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A332" s="9" t="s">
+      <c r="A332" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A333" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A334" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A335" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C335" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="D335" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="B332" s="9" t="s">
+      <c r="E335" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A336" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C336" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="C332" s="9" t="s">
+      <c r="D336" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="D332" s="9" t="s">
+      <c r="E336" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A337" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C337" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="E332" s="25" t="s">
+      <c r="D337" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="E337" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F332" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A333" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B333" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C333" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="D333" s="9" t="s">
+      <c r="F337" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A338" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C338" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="E333" s="25" t="s">
+      <c r="D338" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="E338" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F333" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A334" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B334" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C334" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="D334" s="9" t="s">
+      <c r="F338" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A339" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C339" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="E334" s="25" t="s">
+      <c r="D339" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="E339" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F334" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A335" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B335" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C335" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="D335" s="9" t="s">
+      <c r="F339" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A340" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C340" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="E335" s="25" t="s">
+      <c r="D340" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="E340" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F335" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A336" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B336" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C336" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="D336" s="9" t="s">
+      <c r="F340" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A341" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C341" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="E336" s="25" t="s">
+      <c r="D341" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="E341" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F336" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A337" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B337" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C337" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="D337" s="9" t="s">
+      <c r="F341" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A342" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C342" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="E337" s="25" t="s">
+      <c r="D342" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="E342" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F337" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A338" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B338" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C338" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="D338" s="9" t="s">
+      <c r="F342" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A343" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C343" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="E338" s="25" t="s">
+      <c r="D343" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="E343" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F338" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A339" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B339" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C339" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="D339" s="9" t="s">
+      <c r="F343" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A344" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C344" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="E339" s="25" t="s">
+      <c r="D344" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="E344" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F339" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A340" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B340" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C340" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="D340" s="9" t="s">
+      <c r="F344" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A345" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C345" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="E340" s="25" t="s">
+      <c r="D345" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="E345" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F340" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A341" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B341" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C341" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="D341" s="9" t="s">
+      <c r="F345" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A346" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C346" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="E341" s="25" t="s">
+      <c r="D346" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="E346" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F341" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A342" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B342" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C342" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="D342" s="9" t="s">
+      <c r="F346" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A347" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C347" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="E342" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F342" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A343" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B343" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C343" s="9" t="s">
+      <c r="D347" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="D343" s="9" t="s">
+      <c r="E347" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A348" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C348" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="E343" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F343" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A344" s="9" t="s">
+      <c r="D348" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E348" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A349" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C349" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="D349" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="E349" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A350" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C350" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="D350" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="E350" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A351" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C351" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D351" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E351" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A352" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B352" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C352" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D352" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="E352" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A353" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B353" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D353" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="E353" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A354" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C354" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="D354" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="E354" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A355" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B344" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="C344" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="D344" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="E344" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F344" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A345" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B345" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C345" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D345" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="E345" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F345" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A346" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B346" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C346" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="D346" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="E346" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="F346" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A347" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B347" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C347" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="D347" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="E347" s="25" t="s">
+      <c r="B355" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="C355" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D355" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E355" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A356" s="27" t="s">
+        <v>622</v>
+      </c>
+      <c r="B356" s="28" t="s">
+        <v>623</v>
+      </c>
+      <c r="C356" s="28" t="s">
+        <v>680</v>
+      </c>
+      <c r="D356" s="28" t="s">
+        <v>681</v>
+      </c>
+      <c r="E356" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="F347" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A348" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B348" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C348" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="D348" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="E348" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F348" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A349" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B349" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C349" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="D349" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="E349" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F349" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A350" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="B350" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="C350" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="D350" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="E350" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F350" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A351" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B351" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C351" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="D351" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="E351" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="F351" s="23" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A352" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B352" s="9" t="s">
+      <c r="F356" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C352" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="D352" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="E352" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F352" s="23" t="s">
-        <v>670</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E30:E56 E77:E170 E191:E212 E231:E277 E290:E331 E2:E21" xr:uid="{AA2D0868-0291-7743-87D8-2579833BF515}">
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E30:E56 E192:E213 E232:E279 E292:E334 E2:E21 E77:E115 E117:E171" xr:uid="{AA2D0868-0291-7743-87D8-2579833BF515}">
       <formula1>"학부,대학원,교직원,WC"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="- 없이 입력해주세요." sqref="C30:C56 C77:C114 B110 C116:C170 C191:C202 C213:C230 C241:C277 C239 C232:C237 C290:C331 C2:C21" xr:uid="{4D4B1335-EC85-EE4D-AF36-951BDA12D56A}"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E57:E76 E171:E190" xr:uid="{1BD9A82A-B44A-704E-A436-D5A9E8B9F22B}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="- 없이 입력해주세요." sqref="C30:C56 C292:C334 B110 C192:C203 C118:C171 C243:C279 C241 C234:C239 C214:C232 C2:C21 C77:C115" xr:uid="{4D4B1335-EC85-EE4D-AF36-951BDA12D56A}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E57:E76 E172:E191" xr:uid="{1BD9A82A-B44A-704E-A436-D5A9E8B9F22B}">
+      <formula1>"학부,대학원,교직원,WC"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E356" xr:uid="{5595D424-3439-4946-A515-D0D008CD5BF9}">
       <formula1>"학부,대학원,교직원,WC"</formula1>
     </dataValidation>
   </dataValidations>

--- a/2025-jonghap.xlsx
+++ b/2025-jonghap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/highmac/SnuBaseball/SnuBaseball-back/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF3F48C-EF24-894C-9A72-C92ABAE6BAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02339F4A-7C89-3941-9CDE-0428FF94B3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21600" xr2:uid="{1B457AFA-6E1C-D440-A48D-2A40A7C0C09B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="688">
   <si>
     <t>인문대학</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -2550,6 +2550,15 @@
   <si>
     <t>고재윤</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">사범대학 </t>
+  </si>
+  <si>
+    <t>2021-14610</t>
+  </si>
+  <si>
+    <t>유승현</t>
   </si>
 </sst>
 </file>
@@ -2772,7 +2781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2838,12 +2847,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2854,6 +2857,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5513,19 +5519,19 @@
       <c r="A114" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B114" s="24" t="s">
+      <c r="B114" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C114" s="24">
+      <c r="C114" s="1">
         <v>202129853</v>
       </c>
-      <c r="D114" s="24" t="s">
+      <c r="D114" s="1" t="s">
         <v>674</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F114" s="23" t="s">
+      <c r="F114" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -5565,7 +5571,7 @@
       <c r="E116" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F116" s="23" t="s">
+      <c r="F116" s="1" t="s">
         <v>293</v>
       </c>
     </row>
@@ -7851,21 +7857,21 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="18" t="s">
-        <v>191</v>
+        <v>685</v>
       </c>
       <c r="B231" s="19" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>501</v>
+        <v>686</v>
       </c>
       <c r="D231" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="E231" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F231" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F231" s="27" t="s">
         <v>209</v>
       </c>
     </row>
@@ -7882,7 +7888,7 @@
       <c r="D232" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="E232" s="25" t="s">
+      <c r="E232" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
@@ -9463,7 +9469,7 @@
       <c r="E311" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F311" s="23" t="s">
+      <c r="F311" s="1" t="s">
         <v>606</v>
       </c>
     </row>
@@ -10348,19 +10354,19 @@
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A356" s="27" t="s">
+      <c r="A356" s="25" t="s">
         <v>622</v>
       </c>
-      <c r="B356" s="28" t="s">
+      <c r="B356" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="C356" s="28" t="s">
+      <c r="C356" s="26" t="s">
         <v>680</v>
       </c>
-      <c r="D356" s="28" t="s">
+      <c r="D356" s="26" t="s">
         <v>681</v>
       </c>
-      <c r="E356" s="26" t="s">
+      <c r="E356" s="24" t="s">
         <v>100</v>
       </c>
       <c r="F356" s="1" t="s">
@@ -10372,7 +10378,7 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E30:E56 E192:E213 E232:E279 E292:E334 E2:E21 E77:E115 E117:E171" xr:uid="{AA2D0868-0291-7743-87D8-2579833BF515}">
       <formula1>"학부,대학원,교직원,WC"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="- 없이 입력해주세요." sqref="C30:C56 C292:C334 B110 C192:C203 C118:C171 C243:C279 C241 C234:C239 C214:C232 C2:C21 C77:C115" xr:uid="{4D4B1335-EC85-EE4D-AF36-951BDA12D56A}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="- 없이 입력해주세요." sqref="C30:C56 C292:C334 B110 C192:C203 C118:C171 C243:C279 C241 C234:C239 C2:C21 C77:C115 C214:C232" xr:uid="{4D4B1335-EC85-EE4D-AF36-951BDA12D56A}"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E57:E76 E172:E191" xr:uid="{1BD9A82A-B44A-704E-A436-D5A9E8B9F22B}">
       <formula1>"학부,대학원,교직원,WC"</formula1>
     </dataValidation>
